--- a/Codelist Excel Files and Conversion Templates to XML/progressState.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/progressState.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{6375B485-8464-4B48-93AF-59145BAE8E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4758CD-E860-CD47-A272-4E1827ECF637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9200" yWindow="3280" windowWidth="39400" windowHeight="24940" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9200" yWindow="2280" windowWidth="39400" windowHeight="24940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="302">
   <si>
     <t>Description</t>
   </si>
@@ -930,22 +930,19 @@
     <t>The sample has been safely discarded following analysis or the completion of the retention period.</t>
   </si>
   <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>//diggs:testingProgress//diggs:state</t>
-  </si>
-  <si>
-    <t>//diggs:scheduleProgress//diggs:state</t>
-  </si>
-  <si>
     <t>progressState</t>
   </si>
   <si>
     <t>DIGGS Progress Event State Code Definitions</t>
   </si>
   <si>
-    <t>This dictionary contains standard code values for the state property of the diggs:ProgressEvent object when used within a program. These values serve to define the values used in reporting the status of a workflow chain. Certain terms are only applicable to specific contexts as specified in the sourceelementXpath</t>
+    <t>//diggs:testingProgress//diggs:progressState</t>
+  </si>
+  <si>
+    <t>//diggs:scheduleProgress//diggs:progressState</t>
+  </si>
+  <si>
+    <t>This dictionary contains standard code values for the progressState property of the diggs:ProgressEvent object when used within a program. These values serve to define the values used in reporting the status of a workflow chain. Certain terms are only applicable to specific contexts as specified in the sourceelementXpath</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1106,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1152,19 +1149,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1212,59 +1199,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1435,6 +1369,59 @@
       </font>
       <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
@@ -1449,53 +1436,53 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E4" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DictionaryName" displayName="DictionaryName" ref="A1:E4" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="A1:E4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Start" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dictionary ID" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DictionaryFile" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DictionaryName" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H18" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Definitions" displayName="Definitions" ref="A1:H18" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:H18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H18">
     <sortCondition ref="A1:A18"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Start" dataDxfId="11">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,AssociatedElements!B$2:B2920,1,FALSE)),"Not used","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="ID" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Name" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="DataType" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="QuantityClass" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Authority" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Reference" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D21" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="AssociatedElements" displayName="AssociatedElements" ref="A1:D21" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="A1:D21" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C2">
     <sortCondition ref="C1:C2"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Start" dataDxfId="23">
       <calculatedColumnFormula>IF(ISNA(VLOOKUP(B2,Definitions!B$2:B$1820,1,FALSE)),"Not listed","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="SourceElement" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="ConditionalElement"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1842,13 +1829,13 @@
         <v>297</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17" x14ac:dyDescent="0.2">
@@ -1990,24 +1977,24 @@
       <c r="F5" s="13"/>
       <c r="G5" s="9"/>
     </row>
-    <row r="6" spans="1:8" s="18" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="str">
+    <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="str">
         <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2924,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>281</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="21"/>
+      <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="str">
@@ -2290,7 +2277,7 @@
         <v>246</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2302,7 +2289,7 @@
         <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2314,7 +2301,7 @@
         <v>248</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2326,7 +2313,7 @@
         <v>249</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2338,7 +2325,7 @@
         <v>250</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2350,7 +2337,7 @@
         <v>252</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2362,7 +2349,7 @@
         <v>253</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2374,7 +2361,7 @@
         <v>254</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2386,7 +2373,7 @@
         <v>255</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2398,7 +2385,7 @@
         <v>256</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2410,7 +2397,7 @@
         <v>257</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2422,7 +2409,7 @@
         <v>258</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2434,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2446,7 +2433,7 @@
         <v>260</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
@@ -2458,7 +2445,7 @@
         <v>261</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -2470,55 +2457,55 @@
         <v>277</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="str">
+      <c r="A18" t="str">
         <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1820,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="2" t="s">
         <v>246</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="str">
+      <c r="A19" t="str">
         <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1820,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="str">
+      <c r="A20" t="str">
         <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1820,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="2" t="s">
         <v>251</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="str">
+      <c r="A21" t="str">
         <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1820,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="2" t="s">
         <v>258</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
